--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104155385</v>
+        <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584039</v>
+        <v>584118</v>
       </c>
       <c r="R2" t="n">
-        <v>7047814</v>
+        <v>7047653</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155385</t>
+          <t>https://artportalen.se/Sighting/137012012</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103633885</v>
+        <v>104155385</v>
       </c>
       <c r="B3" t="n">
-        <v>92208</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584075</v>
+        <v>584039</v>
       </c>
       <c r="R3" t="n">
-        <v>7047590</v>
+        <v>7047814</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,12 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,13 +899,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103633885</t>
+          <t>https://artportalen.se/Sighting/104155385</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160881</v>
+        <v>103633885</v>
       </c>
       <c r="B4" t="n">
         <v>92208</v>
@@ -932,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584146</v>
+        <v>584075</v>
       </c>
       <c r="R4" t="n">
-        <v>7047543</v>
+        <v>7047590</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:46</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,13 +1002,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104160881</t>
+          <t>https://artportalen.se/Sighting/103633885</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104161644</v>
+        <v>104160881</v>
       </c>
       <c r="B5" t="n">
         <v>92208</v>
@@ -1045,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584080</v>
+        <v>584146</v>
       </c>
       <c r="R5" t="n">
-        <v>7047594</v>
+        <v>7047543</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,13 +1115,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161644</t>
+          <t>https://artportalen.se/Sighting/104160881</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104161771</v>
+        <v>104161644</v>
       </c>
       <c r="B6" t="n">
         <v>92208</v>
@@ -1158,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584087</v>
+        <v>584080</v>
       </c>
       <c r="R6" t="n">
-        <v>7047616</v>
+        <v>7047594</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,16 +1228,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161771</t>
+          <t>https://artportalen.se/Sighting/104161644</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104155697</v>
+        <v>104161771</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584094</v>
+        <v>584087</v>
       </c>
       <c r="R7" t="n">
-        <v>7047817</v>
+        <v>7047616</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1306,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,55 +1341,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155697</t>
+          <t>https://artportalen.se/Sighting/104161771</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104161701</v>
+        <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>92384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584080</v>
+        <v>584079</v>
       </c>
       <c r="R8" t="n">
-        <v>7047590</v>
+        <v>7047729</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,27 +1442,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161701</t>
+          <t>https://artportalen.se/Sighting/137010334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104161488</v>
+        <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>83173</v>
+        <v>92384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,38 +1470,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584067</v>
+        <v>584103</v>
       </c>
       <c r="R9" t="n">
-        <v>7047577</v>
+        <v>7047587</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,22 +1533,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,27 +1563,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161488</t>
+          <t>https://artportalen.se/Sighting/137012369</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104155958</v>
+        <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>90932</v>
+        <v>92384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,38 +1591,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584180</v>
+        <v>584159</v>
       </c>
       <c r="R10" t="n">
-        <v>7047775</v>
+        <v>7047490</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,12 +1645,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,66 +1675,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155958</t>
+          <t>https://artportalen.se/Sighting/137012812</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104161902</v>
+        <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>93201</v>
+        <v>92384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584052</v>
+        <v>584159</v>
       </c>
       <c r="R11" t="n">
-        <v>7047618</v>
+        <v>7047511</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,12 +1757,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,27 +1787,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161902</t>
+          <t>https://artportalen.se/Sighting/137012906</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115598818</v>
+        <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>91930</v>
+        <v>92384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,37 +1815,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584042</v>
+        <v>584182</v>
       </c>
       <c r="R12" t="n">
-        <v>7047727</v>
+        <v>7047499</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1845,22 +1878,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,27 +1908,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115598818</t>
+          <t>https://artportalen.se/Sighting/137013031</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115600812</v>
+        <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>91930</v>
+        <v>92384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584124</v>
+        <v>584219</v>
       </c>
       <c r="R13" t="n">
-        <v>7047475</v>
+        <v>7047454</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1990,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,38 +2031,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115600812</t>
+          <t>https://artportalen.se/Sighting/137013283</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104155987</v>
+        <v>104155697</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584193</v>
+        <v>584094</v>
       </c>
       <c r="R14" t="n">
-        <v>7047771</v>
+        <v>7047817</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2075,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,55 +2144,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155987</t>
+          <t>https://artportalen.se/Sighting/104155697</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104161842</v>
+        <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>92113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584071</v>
+        <v>584112</v>
       </c>
       <c r="R15" t="n">
-        <v>7047627</v>
+        <v>7047655</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,22 +2215,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,27 +2245,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161842</t>
+          <t>https://artportalen.se/Sighting/137011569</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104160594</v>
+        <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
+        <v>92113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,38 +2273,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584262</v>
+        <v>584123</v>
       </c>
       <c r="R16" t="n">
-        <v>7047511</v>
+        <v>7047650</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,22 +2327,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,27 +2357,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104160594</t>
+          <t>https://artportalen.se/Sighting/137011917</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104369095</v>
+        <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>93235</v>
+        <v>92113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,38 +2385,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584146</v>
+        <v>584106</v>
       </c>
       <c r="R17" t="n">
-        <v>7047818</v>
+        <v>7047590</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2409,22 +2439,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,66 +2469,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104369095</t>
+          <t>https://artportalen.se/Sighting/137012371</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103633678</v>
+        <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>92113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584130</v>
+        <v>584158</v>
       </c>
       <c r="R18" t="n">
-        <v>7047609</v>
+        <v>7047511</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,12 +2551,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,66 +2581,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103633678</t>
+          <t>https://artportalen.se/Sighting/137012883</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103634199</v>
+        <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>92113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>584256</v>
       </c>
       <c r="R19" t="n">
-        <v>7047727</v>
+        <v>7047433</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,12 +2663,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,27 +2693,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103634199</t>
+          <t>https://artportalen.se/Sighting/137013522</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103634296</v>
+        <v>104161701</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584038</v>
+        <v>584080</v>
       </c>
       <c r="R20" t="n">
-        <v>7047762</v>
+        <v>7047590</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2728,17 +2776,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,55 +2817,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103634296</t>
+          <t>https://artportalen.se/Sighting/104161701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104155882</v>
+        <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>92545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584184</v>
+        <v>584106</v>
       </c>
       <c r="R21" t="n">
-        <v>7047793</v>
+        <v>7047588</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2836,22 +2888,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,66 +2918,74 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155882</t>
+          <t>https://artportalen.se/Sighting/137012391</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104155991</v>
+        <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>92545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584193</v>
+        <v>584169</v>
       </c>
       <c r="R22" t="n">
-        <v>7047771</v>
+        <v>7047492</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,27 +3009,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,66 +3039,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155991</t>
+          <t>https://artportalen.se/Sighting/137012999</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104156221</v>
+        <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>92545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584208</v>
+        <v>584256</v>
       </c>
       <c r="R23" t="n">
-        <v>7047743</v>
+        <v>7047432</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3067,27 +3121,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,49 +3151,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104156221</t>
+          <t>https://artportalen.se/Sighting/137013488</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104160885</v>
+        <v>104161488</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3155,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584146</v>
+        <v>584067</v>
       </c>
       <c r="R24" t="n">
-        <v>7047543</v>
+        <v>7047577</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3190,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,38 +3275,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104160885</t>
+          <t>https://artportalen.se/Sighting/104161488</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104369108</v>
+        <v>104155958</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>90932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3268,10 +3317,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584129</v>
+        <v>584180</v>
       </c>
       <c r="R25" t="n">
-        <v>7047823</v>
+        <v>7047775</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3298,22 +3347,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,27 +3367,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104369108</t>
+          <t>https://artportalen.se/Sighting/104155958</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103633624</v>
+        <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>93411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3356,38 +3395,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584121</v>
+        <v>584141</v>
       </c>
       <c r="R26" t="n">
-        <v>7047645</v>
+        <v>7047696</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3411,12 +3449,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,65 +3479,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103633624</t>
+          <t>https://artportalen.se/Sighting/137011347</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115478462</v>
+        <v>104161902</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>93201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584113</v>
+        <v>584052</v>
       </c>
       <c r="R27" t="n">
-        <v>7047657</v>
+        <v>7047618</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3513,22 +3562,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3543,27 +3582,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115478462</t>
+          <t>https://artportalen.se/Sighting/104161902</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104161089</v>
+        <v>115598818</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,38 +3610,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584076</v>
+        <v>584042</v>
       </c>
       <c r="R28" t="n">
-        <v>7047575</v>
+        <v>7047727</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3626,22 +3664,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3656,27 +3694,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161089</t>
+          <t>https://artportalen.se/Sighting/115598818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104161835</v>
+        <v>115600812</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,38 +3722,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584071</v>
+        <v>584124</v>
       </c>
       <c r="R29" t="n">
-        <v>7047627</v>
+        <v>7047475</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3739,22 +3776,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,49 +3806,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161835</t>
+          <t>https://artportalen.se/Sighting/115600812</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104161928</v>
+        <v>104155987</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3822,10 +3859,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584052</v>
+        <v>584193</v>
       </c>
       <c r="R30" t="n">
-        <v>7047618</v>
+        <v>7047771</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3855,9 +3892,19 @@
           <t>2022-10-17</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,16 +3930,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104161928</t>
+          <t>https://artportalen.se/Sighting/104155987</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104157574</v>
+        <v>104161842</v>
       </c>
       <c r="B31" t="n">
-        <v>80460</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3900,21 +3947,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584191</v>
+        <v>584071</v>
       </c>
       <c r="R31" t="n">
-        <v>7047729</v>
+        <v>7047627</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3960,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3970,7 +4017,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3996,59 +4043,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104157574</t>
+          <t>https://artportalen.se/Sighting/104161842</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115477802</v>
+        <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>57953</v>
+        <v>92076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584205</v>
+        <v>584127</v>
       </c>
       <c r="R32" t="n">
-        <v>7047467</v>
+        <v>7047485</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4072,22 +4114,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4102,27 +4144,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115477802</t>
+          <t>https://artportalen.se/Sighting/137012702</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115477919</v>
+        <v>104160594</v>
       </c>
       <c r="B33" t="n">
-        <v>57953</v>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4130,42 +4172,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584186</v>
+        <v>584262</v>
       </c>
       <c r="R33" t="n">
-        <v>7047481</v>
+        <v>7047511</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,22 +4227,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,27 +4257,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115477919</t>
+          <t>https://artportalen.se/Sighting/104160594</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115598342</v>
+        <v>104369095</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,39 +4285,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584036</v>
+        <v>584146</v>
       </c>
       <c r="R34" t="n">
-        <v>7047798</v>
+        <v>7047818</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4306,22 +4340,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,27 +4370,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115598342</t>
+          <t>https://artportalen.se/Sighting/104369095</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115599470</v>
+        <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>93449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,39 +4398,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584055</v>
+        <v>584132</v>
       </c>
       <c r="R35" t="n">
-        <v>7047627</v>
+        <v>7047483</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,22 +4452,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,59 +4493,55 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115599470</t>
+          <t>https://artportalen.se/Sighting/137012697</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115599859</v>
+        <v>103633678</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584084</v>
+        <v>584130</v>
       </c>
       <c r="R36" t="n">
-        <v>7047629</v>
+        <v>7047609</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,22 +4565,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,70 +4585,66 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115599859</t>
+          <t>https://artportalen.se/Sighting/103633678</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115600450</v>
+        <v>103634199</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584104</v>
+        <v>584026</v>
       </c>
       <c r="R37" t="n">
-        <v>7047526</v>
+        <v>7047727</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,22 +4668,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4687,70 +4688,66 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115600450</t>
+          <t>https://artportalen.se/Sighting/103634199</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115600486</v>
+        <v>103634296</v>
       </c>
       <c r="B38" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584098</v>
+        <v>584038</v>
       </c>
       <c r="R38" t="n">
-        <v>7047540</v>
+        <v>7047762</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4774,22 +4771,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4804,70 +4796,66 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115600486</t>
+          <t>https://artportalen.se/Sighting/103634296</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115600902</v>
+        <v>104155882</v>
       </c>
       <c r="B39" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584123</v>
+        <v>584184</v>
       </c>
       <c r="R39" t="n">
-        <v>7047482</v>
+        <v>7047793</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4891,22 +4879,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4921,70 +4909,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115600902</t>
+          <t>https://artportalen.se/Sighting/104155882</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115601374</v>
+        <v>104155991</v>
       </c>
       <c r="B40" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584149</v>
+        <v>584193</v>
       </c>
       <c r="R40" t="n">
-        <v>7047442</v>
+        <v>7047771</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5008,22 +4992,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5038,70 +5027,66 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115601374</t>
+          <t>https://artportalen.se/Sighting/104155991</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115601710</v>
+        <v>104156221</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584185</v>
+        <v>584208</v>
       </c>
       <c r="R41" t="n">
-        <v>7047424</v>
+        <v>7047743</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,22 +5110,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,70 +5145,66 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115601710</t>
+          <t>https://artportalen.se/Sighting/104156221</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115601916</v>
+        <v>104160885</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584210</v>
+        <v>584146</v>
       </c>
       <c r="R42" t="n">
-        <v>7047396</v>
+        <v>7047543</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,22 +5228,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5272,70 +5258,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115601916</t>
+          <t>https://artportalen.se/Sighting/104160885</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115604241</v>
+        <v>104369108</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584185</v>
+        <v>584129</v>
       </c>
       <c r="R43" t="n">
-        <v>7047771</v>
+        <v>7047823</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5359,22 +5341,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5389,71 +5371,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115604241</t>
+          <t>https://artportalen.se/Sighting/104369108</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103634191</v>
+        <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>58114</v>
+        <v>79476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584026</v>
+        <v>584083</v>
       </c>
       <c r="R44" t="n">
-        <v>7047727</v>
+        <v>7047801</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5477,12 +5453,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5497,66 +5483,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103634191</t>
+          <t>https://artportalen.se/Sighting/137010100</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104155621</v>
+        <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>58114</v>
+        <v>79476</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584096</v>
+        <v>584106</v>
       </c>
       <c r="R45" t="n">
-        <v>7047800</v>
+        <v>7047728</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5580,22 +5565,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,27 +5595,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155621</t>
+          <t>https://artportalen.se/Sighting/137010424</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104155966</v>
+        <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>79476</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5638,38 +5623,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584190</v>
+        <v>584137</v>
       </c>
       <c r="R46" t="n">
-        <v>7047745</v>
+        <v>7047725</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5693,22 +5677,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5723,27 +5707,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104155966</t>
+          <t>https://artportalen.se/Sighting/137010552</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104157121</v>
+        <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>79476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5751,38 +5735,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584196</v>
+        <v>584157</v>
       </c>
       <c r="R47" t="n">
-        <v>7047725</v>
+        <v>7047741</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5806,22 +5789,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5836,27 +5819,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104157121</t>
+          <t>https://artportalen.se/Sighting/137011046</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104157530</v>
+        <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>79476</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5864,38 +5847,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584198</v>
+        <v>584144</v>
       </c>
       <c r="R48" t="n">
-        <v>7047725</v>
+        <v>7047698</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5919,22 +5901,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5949,27 +5931,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104157530</t>
+          <t>https://artportalen.se/Sighting/137011371</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104157571</v>
+        <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>79476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,38 +5959,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584196</v>
+        <v>584159</v>
       </c>
       <c r="R49" t="n">
-        <v>7047731</v>
+        <v>7047511</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6032,22 +6013,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,27 +6043,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104157571</t>
+          <t>https://artportalen.se/Sighting/137012916</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104157611</v>
+        <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>79476</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6090,38 +6071,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584187</v>
+        <v>584190</v>
       </c>
       <c r="R50" t="n">
-        <v>7047726</v>
+        <v>7047482</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6145,22 +6125,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6175,18 +6155,4649 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137013164</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>103633624</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>584121</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7047645</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103633624</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115478462</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>584113</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7047657</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115478462</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137012339</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>584102</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7047592</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137012339</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137013314</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>584239</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7047457</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137013314</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>104161089</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>584076</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7047575</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161089</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>104161835</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>584071</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7047627</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161835</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>104161928</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>584052</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7047618</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104161928</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137010236</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>584063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7047729</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137010236</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>104157574</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>584191</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7047729</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157574</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>115477802</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>584205</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7047467</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477802</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>115477919</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>584186</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7047481</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477919</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>115598342</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>584036</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7047798</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115598342</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>115599470</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>584055</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7047627</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115599470</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>115599859</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>584084</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7047629</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115599859</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>115600450</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>584104</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7047526</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jonatan Nordström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600450</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>115600486</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>584098</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7047540</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600486</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>115600902</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>584123</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7047482</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600902</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>115601374</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>584149</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7047442</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601374</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>115601710</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>584185</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7047424</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601710</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>115601916</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>584210</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7047396</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115601916</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115604241</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>584185</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7047771</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115604241</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137010319</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>584077</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7047722</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137010319</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137010337</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>584076</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7047721</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137010337</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137011928</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>584123</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7047648</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137011928</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>137010160</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>584045</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7047729</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137010160</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137010168</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>584045</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7047727</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137010168</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137011352</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>584145</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7047694</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137011352</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>103634191</v>
+      </c>
+      <c r="B78" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>584026</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7047727</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103634191</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>104155621</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>584096</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7047800</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155621</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137013564</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>584242</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7047427</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137013564</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137011610</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>584109</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7047661</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137011610</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>104155966</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>584190</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7047745</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104155966</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>104157121</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>584196</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157121</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>104157530</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>584198</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157530</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>104157571</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>584196</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7047731</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157571</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>104157611</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>584187</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7047726</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/104157611</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137012037</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>584120</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7047651</v>
+      </c>
+      <c r="S87" t="n">
+        <v>20</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137012037</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>137012249</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>584084</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7047622</v>
+      </c>
+      <c r="S88" t="n">
+        <v>20</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137012249</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>137012918</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>584174</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7047503</v>
+      </c>
+      <c r="S89" t="n">
+        <v>20</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137012918</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>137013602</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Skumsåsberget, Skumsåsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>584228</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7047440</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137013602</t>
         </is>
       </c>
     </row>
@@ -6241,6 +10852,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92733</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92737</v>
+        <v>92738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92738</v>
+        <v>92744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92744</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>137010160</v>
       </c>
       <c r="B75" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>137010168</v>
       </c>
       <c r="B76" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>137011352</v>
       </c>
       <c r="B77" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>137010160</v>
       </c>
       <c r="B75" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>137010168</v>
       </c>
       <c r="B76" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>137011352</v>
       </c>
       <c r="B77" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -8598,11 +8598,7 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -8720,11 +8716,7 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -8842,11 +8834,7 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -8964,11 +8952,7 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -9081,11 +9065,7 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -9198,11 +9178,7 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -9540,16 +9516,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>
@@ -9666,16 +9634,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skumsåsberget, Skumsåsberget, Ång</t>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92765</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>137010160</v>
       </c>
       <c r="B75" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>137010168</v>
       </c>
       <c r="B76" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>137011352</v>
       </c>
       <c r="B77" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92778</v>
+        <v>92779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92779</v>
+        <v>92782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>137010160</v>
       </c>
       <c r="B75" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>137010168</v>
       </c>
       <c r="B76" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>137011352</v>
       </c>
       <c r="B77" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92801</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92617</v>
+        <v>92618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92617</v>
+        <v>92618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92617</v>
+        <v>92618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 34269-2022 artfynd.xlsx
+++ b/artfynd/A 34269-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137012012</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>137010334</v>
       </c>
       <c r="B8" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137012369</v>
       </c>
       <c r="B9" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137012812</v>
       </c>
       <c r="B10" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137012906</v>
       </c>
       <c r="B11" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>137013031</v>
       </c>
       <c r="B12" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137013283</v>
       </c>
       <c r="B13" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137011569</v>
       </c>
       <c r="B15" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137011917</v>
       </c>
       <c r="B16" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137012371</v>
       </c>
       <c r="B17" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137012883</v>
       </c>
       <c r="B18" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137013522</v>
       </c>
       <c r="B19" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137012391</v>
       </c>
       <c r="B21" t="n">
-        <v>92618</v>
+        <v>92621</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>137012999</v>
       </c>
       <c r="B22" t="n">
-        <v>92618</v>
+        <v>92621</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>137013488</v>
       </c>
       <c r="B23" t="n">
-        <v>92618</v>
+        <v>92621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137011347</v>
       </c>
       <c r="B26" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>137012702</v>
       </c>
       <c r="B32" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137012697</v>
       </c>
       <c r="B35" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>137010100</v>
       </c>
       <c r="B44" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>137010424</v>
       </c>
       <c r="B45" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>137010552</v>
       </c>
       <c r="B46" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>137011046</v>
       </c>
       <c r="B47" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137011371</v>
       </c>
       <c r="B48" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137012916</v>
       </c>
       <c r="B49" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>137013164</v>
       </c>
       <c r="B50" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>137012339</v>
       </c>
       <c r="B53" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>137013314</v>
       </c>
       <c r="B54" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>137010236</v>
       </c>
       <c r="B58" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>137010319</v>
       </c>
       <c r="B72" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>137010337</v>
       </c>
       <c r="B73" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>137011928</v>
       </c>
       <c r="B74" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>137010160</v>
       </c>
       <c r="B75" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>137010168</v>
       </c>
       <c r="B76" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>137011352</v>
       </c>
       <c r="B77" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>137013564</v>
       </c>
       <c r="B80" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>137011610</v>
       </c>
       <c r="B81" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>137012037</v>
       </c>
       <c r="B87" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137012249</v>
       </c>
       <c r="B88" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>137012918</v>
       </c>
       <c r="B89" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137013602</v>
       </c>
       <c r="B90" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
